--- a/result/FAT1_LUSC_Tables.xlsx
+++ b/result/FAT1_LUSC_Tables.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,22 +438,23 @@
           <t>Clinical Characteristics</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr"/>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -469,6 +470,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -477,17 +479,20 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3" t="n">
         <v>0</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>64</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>110</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.013</t>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.026</t>
         </is>
       </c>
     </row>
@@ -498,15 +503,18 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>29</v>
+      </c>
+      <c r="C4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>136</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>133</v>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -518,6 +526,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -526,17 +535,20 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C6" t="n">
         <v>0</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>44</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>71</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.189</t>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.340</t>
         </is>
       </c>
     </row>
@@ -547,15 +559,18 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>33</v>
+      </c>
+      <c r="C7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>156</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>172</v>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -567,6 +582,7 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -575,17 +591,20 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>95</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>122</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.500</t>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0.457</t>
         </is>
       </c>
     </row>
@@ -596,15 +615,18 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>15</v>
+      </c>
+      <c r="C10" t="n">
         <v>0</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>72</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>69</v>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -613,15 +635,18 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" t="n">
         <v>0</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>28</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>48</v>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -630,15 +655,18 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="n">
         <v>0</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>2</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>3</v>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -650,6 +678,7 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -658,17 +687,20 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>34</v>
+      </c>
+      <c r="C14" t="n">
         <v>0</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>166</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>201</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0.815</t>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0.174</t>
         </is>
       </c>
     </row>
@@ -679,15 +711,18 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
         <v>0</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>2</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>3</v>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -699,6 +734,7 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -707,17 +743,20 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>30</v>
+      </c>
+      <c r="C17" t="n">
         <v>1</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>127</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>153</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0.869</t>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0.942</t>
         </is>
       </c>
     </row>
@@ -728,15 +767,18 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" t="n">
         <v>0</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>54</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>62</v>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -745,15 +787,18 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" t="n">
         <v>0</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>14</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>22</v>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -765,12 +810,15 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
         <v>1</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>4</v>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -782,6 +830,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -790,17 +839,20 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>13</v>
+      </c>
+      <c r="C22" t="n">
         <v>0</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>38</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>58</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0.568</t>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0.678</t>
         </is>
       </c>
     </row>
@@ -811,15 +863,18 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C23" t="n">
         <v>1</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>129</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>134</v>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -828,15 +883,18 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>7</v>
+      </c>
+      <c r="C24" t="n">
         <v>0</v>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>24</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>39</v>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -845,15 +903,18 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" t="n">
         <v>0</v>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>9</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>12</v>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -865,6 +926,7 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -873,17 +935,20 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>9</v>
+      </c>
+      <c r="C27" t="n">
         <v>0</v>
       </c>
-      <c r="C27" t="n">
+      <c r="D27" t="n">
         <v>32</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>35</v>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0.813</t>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0.731</t>
         </is>
       </c>
     </row>
@@ -894,15 +959,18 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>35</v>
+      </c>
+      <c r="C28" t="n">
         <v>1</v>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>168</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>209</v>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1749,7 +1817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1782,21 +1850,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ageG</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.312</v>
+        <v>1.021</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9370000000000001</v>
+        <v>1.001</v>
       </c>
       <c r="D2" t="n">
-        <v>1.837</v>
+        <v>1.04</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>0.039</t>
         </is>
       </c>
     </row>
@@ -1807,101 +1875,269 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>1.001</v>
       </c>
       <c r="C3" t="n">
-        <v>0.995</v>
+        <v>0.996</v>
       </c>
       <c r="D3" t="n">
-        <v>1.005</v>
+        <v>1.006</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.955</t>
+          <t>0.719</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pathologic_stage</t>
+          <t>TP53Expression</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.213</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.472</v>
+        <v>1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.050</t>
+          <t>0.796</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FAT1group_High</t>
+          <t>CDKN2AExpression</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.572</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.077</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.235</v>
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.584</t>
+          <t>0.954</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FAT1group_Low</t>
+          <t>SOX2Expression</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.423</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0.057</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.137</v>
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.220</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>PIK3CAExpression</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.674</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NOTCH1Expression</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.827</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FAT1group_H</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.595</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.204</v>
+      </c>
+      <c r="D9" t="n">
+        <v>12.488</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.657</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FAT1group_High</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.776</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.862</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FAT1group_Low</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.399</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.450</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>gender_MALE</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>1.185</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.828</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1.696</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0.352</t>
+      <c r="B12" t="n">
+        <v>1.219</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.851</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.747</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0.280</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>pathologic_stage_2.0</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.067</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.523</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0.719</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>pathologic_stage_3.0</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.089</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0.099</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>pathologic_stage_4.0</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.302</v>
+      </c>
+      <c r="D15" t="n">
+        <v>8.314</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0.012</t>
         </is>
       </c>
     </row>
@@ -1916,7 +2152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1948,7 +2184,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <f>== [ Model: Pathologic Stage ] ===</f>
+        <f>== [ Model: Base Model (No Stage) ] ===</f>
         <v/>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -1979,7 +2215,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FAT1expression ~ age + C(gender) + number_pack_years_smoked + C(pathologic_stage)</t>
+          <t>FAT1expression ~ age + number_pack_years_smoked + pathologic_stage + C(gender)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -1994,7 +2230,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.0267</t>
+          <t>0.0167</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -2009,7 +2245,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.2481e-01</t>
+          <t>1.8023e-01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -2034,17 +2270,17 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1478.7825</v>
+        <v>1617.3958</v>
       </c>
       <c r="C8" t="n">
-        <v>-370.2566</v>
+        <v>-297.3177</v>
       </c>
       <c r="D8" t="n">
-        <v>3327.8216</v>
+        <v>3532.1094</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>0.098</t>
         </is>
       </c>
     </row>
@@ -2055,138 +2291,126 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>241.6368</v>
+        <v>254.4179</v>
       </c>
       <c r="C9" t="n">
-        <v>-244.1157</v>
+        <v>-231.4554</v>
       </c>
       <c r="D9" t="n">
-        <v>727.3894</v>
+        <v>740.2913</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>0.304</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C(pathologic_stage)[T.2.0]</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>340.8031</v>
+        <v>29.2325</v>
       </c>
       <c r="C10" t="n">
-        <v>-145.2397</v>
+        <v>3.2563</v>
       </c>
       <c r="D10" t="n">
-        <v>826.8458000000001</v>
+        <v>55.2087</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>0.028</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C(pathologic_stage)[T.3.0]</t>
+          <t>number_pack_years_smoked</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-272.6642</v>
+        <v>0.523</v>
       </c>
       <c r="C11" t="n">
-        <v>-874.4541</v>
+        <v>-6.4573</v>
       </c>
       <c r="D11" t="n">
-        <v>329.1257</v>
+        <v>7.5032</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>0.883</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C(pathologic_stage)[T.4.0]</t>
+          <t>pathologic_stage</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>54.3746</v>
+        <v>-41.3497</v>
       </c>
       <c r="C12" t="n">
-        <v>-2032.4644</v>
+        <v>-314.1214</v>
       </c>
       <c r="D12" t="n">
-        <v>2141.2135</v>
+        <v>231.422</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.959</t>
+          <t>0.766</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>29.538</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3.5317</v>
-      </c>
-      <c r="D13" t="n">
-        <v>55.5442</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0.026</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.4836</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-6.4872</v>
-      </c>
-      <c r="D14" t="n">
-        <v>7.4543</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0.892</t>
-        </is>
-      </c>
+      <c r="A14">
+        <f>== [ Model: Base + Pathologic T ] ===</f>
+        <v/>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>FAT1expression</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16">
-        <f>== [ Model: Pathologic T ] ===</f>
-        <v/>
-      </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FAT1expression ~ age + number_pack_years_smoked + pathologic_stage + C(gender) + C(pathologic_T)</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
@@ -2194,12 +2418,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dependent Variable (Y)</t>
+          <t>R-squared</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FAT1expression</t>
+          <t>0.0252</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -2209,12 +2433,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Model Formula</t>
+          <t>Prob (F-statistic)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FAT1expression ~ age + C(gender) + number_pack_years_smoked + C(pathologic_T)</t>
+          <t>2.2440e-01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -2224,14 +2448,10 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.0253</t>
-        </is>
-      </c>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
@@ -2239,189 +2459,199 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1.4421e-01</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1345.4284</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-604.9032</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3295.76</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0.176</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>202.8292</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-287.3633</v>
+      </c>
+      <c r="D21" t="n">
+        <v>693.0216</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0.416</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Intercept</t>
+          <t>C(pathologic_T)[T.2.0]</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1338.549</v>
+        <v>412.7471</v>
       </c>
       <c r="C22" t="n">
-        <v>-483.2429</v>
+        <v>-133.5957</v>
       </c>
       <c r="D22" t="n">
-        <v>3160.3409</v>
+        <v>959.0898</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>0.138</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C(gender)[T.MALE]</t>
+          <t>C(pathologic_T)[T.3.0]</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>208.6214</v>
+        <v>113.3668</v>
       </c>
       <c r="C23" t="n">
-        <v>-278.1604</v>
+        <v>-749.5174</v>
       </c>
       <c r="D23" t="n">
-        <v>695.4032</v>
+        <v>976.2509</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.796</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C(pathologic_T)[T.2.0]</t>
+          <t>C(pathologic_T)[T.4.0]</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>414.5793</v>
+        <v>-137.4484</v>
       </c>
       <c r="C24" t="n">
-        <v>-115.2272</v>
+        <v>-1457.6134</v>
       </c>
       <c r="D24" t="n">
-        <v>944.3859</v>
+        <v>1182.7166</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.838</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C(pathologic_T)[T.3.0]</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>109.443</v>
+        <v>29.0212</v>
       </c>
       <c r="C25" t="n">
-        <v>-636.0519</v>
+        <v>2.9099</v>
       </c>
       <c r="D25" t="n">
-        <v>854.938</v>
+        <v>55.1325</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.773</t>
+          <t>0.029</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C(pathologic_T)[T.4.0]</t>
+          <t>number_pack_years_smoked</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-152.235</v>
+        <v>0.6377</v>
       </c>
       <c r="C26" t="n">
-        <v>-1308.4665</v>
+        <v>-6.3545</v>
       </c>
       <c r="D26" t="n">
-        <v>1003.9965</v>
+        <v>7.6299</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.796</t>
+          <t>0.858</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>pathologic_stage</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>28.9935</v>
+        <v>-7.9443</v>
       </c>
       <c r="C27" t="n">
-        <v>3.3482</v>
+        <v>-344.2605</v>
       </c>
       <c r="D27" t="n">
-        <v>54.6388</v>
+        <v>328.3719</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>0.963</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>0.5488</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-6.3872</v>
-      </c>
-      <c r="D28" t="n">
-        <v>7.4848</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0.876</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29">
+        <f>== [ Model: Base + Pathologic N ] ===</f>
+        <v/>
+      </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30">
-        <f>== [ Model: Pathologic N ] ===</f>
-        <v/>
-      </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>FAT1expression</t>
+        </is>
+      </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
@@ -2429,12 +2659,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dependent Variable (Y)</t>
+          <t>Model Formula</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FAT1expression</t>
+          <t>FAT1expression ~ age + number_pack_years_smoked + pathologic_stage + C(gender) + C(pathologic_N)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -2444,12 +2674,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Model Formula</t>
+          <t>R-squared</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FAT1expression ~ age + C(gender) + number_pack_years_smoked + C(pathologic_N)</t>
+          <t>0.0270</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -2459,12 +2689,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>R-squared</t>
+          <t>Prob (F-statistic)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0.0256</t>
+          <t>1.8904e-01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -2474,14 +2704,10 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1.4472e-01</t>
-        </is>
-      </c>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
@@ -2489,158 +2715,168 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1734.0277</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-212.9535</v>
+      </c>
+      <c r="D35" t="n">
+        <v>3681.0088</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0.081</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Intercept</t>
+          <t>C(gender)[T.MALE]</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1557.4644</v>
+        <v>256.2397</v>
       </c>
       <c r="C36" t="n">
-        <v>-299.0622</v>
+        <v>-231.4476</v>
       </c>
       <c r="D36" t="n">
-        <v>3413.991</v>
+        <v>743.9271</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.100</t>
+          <t>0.302</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C(gender)[T.MALE]</t>
+          <t>C(pathologic_N)[T.1.0]</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>251.4308</v>
+        <v>364.8938</v>
       </c>
       <c r="C37" t="n">
-        <v>-231.8537</v>
+        <v>-304.0984</v>
       </c>
       <c r="D37" t="n">
-        <v>734.7153</v>
+        <v>1033.8859</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>0.284</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C(pathologic_N)[T.1.0]</t>
+          <t>C(pathologic_N)[T.2.0]</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>195.7305</v>
+        <v>286.9821</v>
       </c>
       <c r="C38" t="n">
-        <v>-296.4388</v>
+        <v>-841.8081</v>
       </c>
       <c r="D38" t="n">
-        <v>687.8998</v>
+        <v>1415.7724</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>0.617</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C(pathologic_N)[T.2.0]</t>
+          <t>C(pathologic_N)[T.3.0]</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>19.7153</v>
+        <v>-1423.1931</v>
       </c>
       <c r="C39" t="n">
-        <v>-781.175</v>
+        <v>-3440.2646</v>
       </c>
       <c r="D39" t="n">
-        <v>820.6056</v>
+        <v>593.8784000000001</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.961</t>
+          <t>0.166</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C(pathologic_N)[T.3.0]</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1711.269</v>
+        <v>29.1434</v>
       </c>
       <c r="C40" t="n">
-        <v>-3566.0426</v>
+        <v>2.6672</v>
       </c>
       <c r="D40" t="n">
-        <v>143.5047</v>
+        <v>55.6197</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.070</t>
+          <t>0.031</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>number_pack_years_smoked</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>28.9646</v>
+        <v>0.0539</v>
       </c>
       <c r="C41" t="n">
-        <v>2.7226</v>
+        <v>-6.9384</v>
       </c>
       <c r="D41" t="n">
-        <v>55.2065</v>
+        <v>7.0462</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>0.988</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>number_pack_years_smoked</t>
+          <t>pathologic_stage</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.0105</v>
+        <v>-161.0707</v>
       </c>
       <c r="C42" t="n">
-        <v>-6.9556</v>
+        <v>-603.7436</v>
       </c>
       <c r="D42" t="n">
-        <v>6.9345</v>
+        <v>281.6022</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.998</t>
+          <t>0.475</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2889,7 @@
     </row>
     <row r="44">
       <c r="A44">
-        <f>== [ Model: Pathologic M ] ===</f>
+        <f>== [ Model: Base + Pathologic M ] ===</f>
         <v/>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2684,7 +2920,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FAT1expression ~ age + C(gender) + number_pack_years_smoked + C(pathologic_M)</t>
+          <t>FAT1expression ~ age + number_pack_years_smoked + pathologic_stage + C(gender) + C(pathologic_M)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -2699,7 +2935,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0.0210</t>
+          <t>0.0207</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -2714,7 +2950,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.5350e-01</t>
+          <t>2.5655e-01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -2739,17 +2975,17 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1188.0899</v>
+        <v>1198.7172</v>
       </c>
       <c r="C50" t="n">
-        <v>-852.7336</v>
+        <v>-991.3101</v>
       </c>
       <c r="D50" t="n">
-        <v>3228.9133</v>
+        <v>3388.7445</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>0.282</t>
         </is>
       </c>
     </row>
@@ -2760,17 +2996,17 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>378.2133</v>
+        <v>374.5121</v>
       </c>
       <c r="C51" t="n">
-        <v>-161.3679</v>
+        <v>-168.5072</v>
       </c>
       <c r="D51" t="n">
-        <v>917.7944</v>
+        <v>917.5314</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>0.176</t>
         </is>
       </c>
     </row>
@@ -2781,17 +3017,17 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-20.5479</v>
+        <v>-10.19</v>
       </c>
       <c r="C52" t="n">
-        <v>-2129.5254</v>
+        <v>-2257.5408</v>
       </c>
       <c r="D52" t="n">
-        <v>2088.4297</v>
+        <v>2237.1608</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0.985</t>
+          <t>0.993</t>
         </is>
       </c>
     </row>
@@ -2802,17 +3038,17 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>32.1441</v>
+        <v>32.0019</v>
       </c>
       <c r="C53" t="n">
-        <v>3.0676</v>
+        <v>2.4734</v>
       </c>
       <c r="D53" t="n">
-        <v>61.2206</v>
+        <v>61.5303</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.030</t>
+          <t>0.034</t>
         </is>
       </c>
     </row>
@@ -2823,26 +3059,47 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1.5819</v>
+        <v>1.6448</v>
       </c>
       <c r="C54" t="n">
-        <v>-6.2226</v>
+        <v>-6.2088</v>
       </c>
       <c r="D54" t="n">
-        <v>9.3863</v>
+        <v>9.4983</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0.690</t>
+          <t>0.681</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>pathologic_stage</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>-2.463</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-316.7788</v>
+      </c>
+      <c r="D55" t="n">
+        <v>311.8528</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0.988</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/result/FAT1_LUSC_Tables.xlsx
+++ b/result/FAT1_LUSC_Tables.xlsx
@@ -1817,7 +1817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1857,14 +1857,14 @@
         <v>1.021</v>
       </c>
       <c r="C2" t="n">
-        <v>1.001</v>
+        <v>1.002</v>
       </c>
       <c r="D2" t="n">
         <v>1.04</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>0.029</t>
         </is>
       </c>
     </row>
@@ -1875,269 +1875,122 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
         <v>0.996</v>
       </c>
       <c r="D3" t="n">
-        <v>1.006</v>
+        <v>1.005</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>0.920</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TP53Expression</t>
+          <t>pathologic_stage</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>1.202</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>1.003</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>1.442</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.796</t>
+          <t>0.047</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CDKN2AExpression</t>
+          <t>FAT1group_H</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>1.596</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0.207</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>12.314</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.954</t>
+          <t>0.654</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SOX2Expression</t>
+          <t>FAT1group_High</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>1.024</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0.61</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>1.718</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.220</t>
+          <t>0.929</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PIK3CAExpression</t>
+          <t>FAT1group_Low</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0.755</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0.452</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>1.261</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.674</t>
+          <t>0.283</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NOTCH1Expression</t>
+          <t>gender_MALE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>1.224</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0.864</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>1.732</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.827</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>FAT1group_H</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1.595</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.204</v>
-      </c>
-      <c r="D9" t="n">
-        <v>12.488</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.657</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>FAT1group_High</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1.048</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.618</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.776</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.862</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>FAT1group_Low</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.469</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1.399</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.450</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>gender_MALE</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.219</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.851</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.747</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0.280</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>pathologic_stage_2.0</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.067</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.748</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1.523</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0.719</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>pathologic_stage_3.0</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.9379999999999999</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2.089</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0.099</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>pathologic_stage_4.0</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1.302</v>
-      </c>
-      <c r="D15" t="n">
-        <v>8.314</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0.012</t>
+          <t>0.256</t>
         </is>
       </c>
     </row>

--- a/result/FAT1_LUSC_Tables.xlsx
+++ b/result/FAT1_LUSC_Tables.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,23 +438,17 @@
           <t>Clinical Characteristics</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr"/>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -469,8 +463,6 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -479,20 +471,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>64</v>
-      </c>
-      <c r="E3" t="n">
         <v>110</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0.026</t>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.004</t>
         </is>
       </c>
     </row>
@@ -503,18 +489,12 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29</v>
+        <v>165</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>136</v>
-      </c>
-      <c r="E4" t="n">
         <v>133</v>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -525,8 +505,6 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -535,20 +513,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>44</v>
-      </c>
-      <c r="E6" t="n">
         <v>71</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0.340</t>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.093</t>
         </is>
       </c>
     </row>
@@ -559,18 +531,12 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33</v>
+        <v>189</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>156</v>
-      </c>
-      <c r="E7" t="n">
         <v>172</v>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -581,8 +547,6 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -591,20 +555,14 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>116</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>95</v>
-      </c>
-      <c r="E9" t="n">
         <v>122</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0.457</t>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.241</t>
         </is>
       </c>
     </row>
@@ -615,18 +573,12 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>72</v>
-      </c>
-      <c r="E10" t="n">
         <v>69</v>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -635,18 +587,12 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>28</v>
-      </c>
-      <c r="E11" t="n">
         <v>48</v>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -655,18 +601,12 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" t="n">
         <v>3</v>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -677,8 +617,6 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -687,20 +625,14 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34</v>
+        <v>199</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>166</v>
-      </c>
-      <c r="E14" t="n">
         <v>201</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0.174</t>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.698</t>
         </is>
       </c>
     </row>
@@ -711,18 +643,12 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" t="n">
         <v>3</v>
       </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -733,8 +659,6 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -743,20 +667,14 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30</v>
+        <v>157</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="n">
-        <v>127</v>
-      </c>
-      <c r="E17" t="n">
         <v>153</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>0.942</t>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0.516</t>
         </is>
       </c>
     </row>
@@ -767,18 +685,12 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>54</v>
-      </c>
-      <c r="E18" t="n">
         <v>62</v>
       </c>
-      <c r="F18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -787,18 +699,12 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>14</v>
-      </c>
-      <c r="E19" t="n">
         <v>22</v>
       </c>
-      <c r="F19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -807,18 +713,12 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="n">
         <v>4</v>
       </c>
-      <c r="F20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -829,8 +729,6 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -839,20 +737,14 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>38</v>
-      </c>
-      <c r="E22" t="n">
         <v>58</v>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>0.678</t>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.424</t>
         </is>
       </c>
     </row>
@@ -863,18 +755,12 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>22</v>
+        <v>152</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="n">
-        <v>129</v>
-      </c>
-      <c r="E23" t="n">
         <v>134</v>
       </c>
-      <c r="F23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -883,18 +769,12 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>24</v>
-      </c>
-      <c r="E24" t="n">
         <v>39</v>
       </c>
-      <c r="F24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -903,18 +783,12 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="n">
-        <v>9</v>
-      </c>
-      <c r="E25" t="n">
         <v>12</v>
       </c>
-      <c r="F25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -925,8 +799,6 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -935,20 +807,14 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" t="n">
-        <v>32</v>
-      </c>
-      <c r="E27" t="n">
         <v>35</v>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>0.731</t>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0.454</t>
         </is>
       </c>
     </row>
@@ -959,18 +825,12 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>35</v>
+        <v>203</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="n">
-        <v>168</v>
-      </c>
-      <c r="E28" t="n">
         <v>209</v>
       </c>
-      <c r="F28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1056,37 +916,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>0.053</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-0.002</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.107</t>
+          <t>-0.038</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.124</t>
+          <t>-0.185</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>0.030</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.200</t>
+          <t>0.190</t>
         </is>
       </c>
     </row>
@@ -1100,32 +960,32 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.723</t>
+          <t>0.816</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>0.242</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>0.964</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>0.399</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>0.509</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1147,7 +1007,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1195,7 +1055,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.723</t>
+          <t>0.816</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -1243,7 +1103,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>0.053</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1291,7 +1151,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>0.242</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1339,7 +1199,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-0.002</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1387,7 +1247,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>0.964</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1435,7 +1295,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.107</t>
+          <t>-0.038</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1483,7 +1343,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>0.399</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1531,7 +1391,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.124</t>
+          <t>-0.185</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1579,7 +1439,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1627,7 +1487,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>0.030</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1675,7 +1535,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>0.509</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1723,7 +1583,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.200</t>
+          <t>0.190</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1854,17 +1714,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.021</v>
+        <v>1.02</v>
       </c>
       <c r="C2" t="n">
-        <v>1.002</v>
+        <v>1.001</v>
       </c>
       <c r="D2" t="n">
-        <v>1.04</v>
+        <v>1.039</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>0.038</t>
         </is>
       </c>
     </row>
@@ -1885,112 +1745,112 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.920</t>
+          <t>0.891</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pathologic_stage</t>
+          <t>FAT1group_Low</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.202</v>
+        <v>0.723</v>
       </c>
       <c r="C4" t="n">
-        <v>1.003</v>
+        <v>0.537</v>
       </c>
       <c r="D4" t="n">
-        <v>1.442</v>
+        <v>0.972</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>0.032</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FAT1group_H</t>
+          <t>gender_MALE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.596</v>
+        <v>1.217</v>
       </c>
       <c r="C5" t="n">
-        <v>0.207</v>
+        <v>0.858</v>
       </c>
       <c r="D5" t="n">
-        <v>12.314</v>
+        <v>1.726</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.654</t>
+          <t>0.270</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FAT1group_High</t>
+          <t>pathologic_stage_2.0</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.024</v>
+        <v>1.002</v>
       </c>
       <c r="C6" t="n">
-        <v>0.61</v>
+        <v>0.706</v>
       </c>
       <c r="D6" t="n">
-        <v>1.718</v>
+        <v>1.422</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.929</t>
+          <t>0.990</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FAT1group_Low</t>
+          <t>pathologic_stage_3.0</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.755</v>
+        <v>1.355</v>
       </c>
       <c r="C7" t="n">
-        <v>0.452</v>
+        <v>0.912</v>
       </c>
       <c r="D7" t="n">
-        <v>1.261</v>
+        <v>2.014</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.283</t>
+          <t>0.132</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>gender_MALE</t>
+          <t>pathologic_stage_4.0</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.224</v>
+        <v>3.157</v>
       </c>
       <c r="C8" t="n">
-        <v>0.864</v>
+        <v>1.262</v>
       </c>
       <c r="D8" t="n">
-        <v>1.732</v>
+        <v>7.896</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>0.014</t>
         </is>
       </c>
     </row>
@@ -2005,7 +1865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2068,7 +1928,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FAT1expression ~ age + number_pack_years_smoked + pathologic_stage + C(gender)</t>
+          <t>FAT1expression ~ age + number_pack_years_smoked + C(gender)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -2083,7 +1943,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.0167</t>
+          <t>0.0035</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -2098,7 +1958,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.8023e-01</t>
+          <t>6.9624e-01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -2123,17 +1983,17 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1617.3958</v>
+        <v>2567.2399</v>
       </c>
       <c r="C8" t="n">
-        <v>-297.3177</v>
+        <v>-816.0096</v>
       </c>
       <c r="D8" t="n">
-        <v>3532.1094</v>
+        <v>5950.4894</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>0.137</t>
         </is>
       </c>
     </row>
@@ -2144,17 +2004,17 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>254.4179</v>
+        <v>139.162</v>
       </c>
       <c r="C9" t="n">
-        <v>-231.4554</v>
+        <v>-777.7317</v>
       </c>
       <c r="D9" t="n">
-        <v>740.2913</v>
+        <v>1056.0557</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>0.766</t>
         </is>
       </c>
     </row>
@@ -2165,17 +2025,17 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29.2325</v>
+        <v>28.2069</v>
       </c>
       <c r="C10" t="n">
-        <v>3.2563</v>
+        <v>-20.2</v>
       </c>
       <c r="D10" t="n">
-        <v>55.2087</v>
+        <v>76.6139</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>0.253</t>
         </is>
       </c>
     </row>
@@ -2186,54 +2046,48 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.523</v>
+        <v>0.9254</v>
       </c>
       <c r="C11" t="n">
-        <v>-6.4573</v>
+        <v>-11.9866</v>
       </c>
       <c r="D11" t="n">
-        <v>7.5032</v>
+        <v>13.8375</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.883</t>
+          <t>0.888</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>pathologic_stage</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>-41.3497</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-314.1214</v>
-      </c>
-      <c r="D12" t="n">
-        <v>231.422</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0.766</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13">
+        <f>== [ Model: Base + Pathologic Stage ] ===</f>
+        <v/>
+      </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14">
-        <f>== [ Model: Base + Pathologic T ] ===</f>
-        <v/>
-      </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>FAT1expression</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
@@ -2241,12 +2095,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dependent Variable (Y)</t>
+          <t>Model Formula</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FAT1expression</t>
+          <t>FAT1expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_stage)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -2256,12 +2110,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Model Formula</t>
+          <t>R-squared</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FAT1expression ~ age + number_pack_years_smoked + pathologic_stage + C(gender) + C(pathologic_T)</t>
+          <t>0.0181</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -2271,12 +2125,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R-squared</t>
+          <t>Prob (F-statistic)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.0252</t>
+          <t>2.8871e-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -2286,14 +2140,10 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2.2440e-01</t>
-        </is>
-      </c>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
@@ -2301,195 +2151,193 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2588.9245</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-884.619</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6062.468</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0.144</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Intercept</t>
+          <t>C(gender)[T.MALE]</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1345.4284</v>
+        <v>72.7373</v>
       </c>
       <c r="C20" t="n">
-        <v>-604.9032</v>
+        <v>-849.0967000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>3295.76</v>
+        <v>994.5713</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.877</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C(gender)[T.MALE]</t>
+          <t>C(pathologic_stage)[T.2.0]</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>202.8292</v>
+        <v>614.3365</v>
       </c>
       <c r="C21" t="n">
-        <v>-287.3633</v>
+        <v>-301.0698</v>
       </c>
       <c r="D21" t="n">
-        <v>693.0216</v>
+        <v>1529.7428</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>0.188</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C(pathologic_T)[T.2.0]</t>
+          <t>C(pathologic_stage)[T.3.0]</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>412.7471</v>
+        <v>-562.1844</v>
       </c>
       <c r="C22" t="n">
-        <v>-133.5957</v>
+        <v>-1702.6774</v>
       </c>
       <c r="D22" t="n">
-        <v>959.0898</v>
+        <v>578.3086</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>0.333</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C(pathologic_T)[T.3.0]</t>
+          <t>C(pathologic_stage)[T.4.0]</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>113.3668</v>
+        <v>2564.0666</v>
       </c>
       <c r="C23" t="n">
-        <v>-749.5174</v>
+        <v>-812.3525</v>
       </c>
       <c r="D23" t="n">
-        <v>976.2509</v>
+        <v>5940.4856</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.796</t>
+          <t>0.136</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C(pathologic_T)[T.4.0]</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-137.4484</v>
+        <v>26.3274</v>
       </c>
       <c r="C24" t="n">
-        <v>-1457.6134</v>
+        <v>-22.5987</v>
       </c>
       <c r="D24" t="n">
-        <v>1182.7166</v>
+        <v>75.2535</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.838</t>
+          <t>0.291</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>number_pack_years_smoked</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>29.0212</v>
+        <v>1.2873</v>
       </c>
       <c r="C25" t="n">
-        <v>2.9099</v>
+        <v>-11.6663</v>
       </c>
       <c r="D25" t="n">
-        <v>55.1325</v>
+        <v>14.2408</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>0.845</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>0.6377</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-6.3545</v>
-      </c>
-      <c r="D26" t="n">
-        <v>7.6299</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0.858</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>pathologic_stage</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>-7.9443</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-344.2605</v>
-      </c>
-      <c r="D27" t="n">
-        <v>328.3719</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0.963</t>
-        </is>
-      </c>
+      <c r="A27">
+        <f>== [ Model: Base + Pathologic T ] ===</f>
+        <v/>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FAT1expression</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29">
-        <f>== [ Model: Base + Pathologic N ] ===</f>
-        <v/>
-      </c>
-      <c r="B29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FAT1expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_T)</t>
+        </is>
+      </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
@@ -2497,12 +2345,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Dependent Variable (Y)</t>
+          <t>R-squared</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FAT1expression</t>
+          <t>0.0071</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -2512,12 +2360,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Model Formula</t>
+          <t>Prob (F-statistic)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FAT1expression ~ age + number_pack_years_smoked + pathologic_stage + C(gender) + C(pathologic_N)</t>
+          <t>8.2118e-01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -2527,14 +2375,10 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>0.0270</t>
-        </is>
-      </c>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
@@ -2542,210 +2386,208 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1.8904e-01</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2951.5437</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-503.003</v>
+      </c>
+      <c r="D33" t="n">
+        <v>6406.0904</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0.094</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>173.4211</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-757.5424</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1104.3846</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0.714</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Intercept</t>
+          <t>C(pathologic_T)[T.2.0]</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1734.0277</v>
+        <v>-384.7719</v>
       </c>
       <c r="C35" t="n">
-        <v>-212.9535</v>
+        <v>-1380.9682</v>
       </c>
       <c r="D35" t="n">
-        <v>3681.0088</v>
+        <v>611.4244</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>0.448</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C(gender)[T.MALE]</t>
+          <t>C(pathologic_T)[T.3.0]</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>256.2397</v>
+        <v>-852.4938</v>
       </c>
       <c r="C36" t="n">
-        <v>-231.4476</v>
+        <v>-2260.3518</v>
       </c>
       <c r="D36" t="n">
-        <v>743.9271</v>
+        <v>555.3643</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>0.235</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C(pathologic_N)[T.1.0]</t>
+          <t>C(pathologic_T)[T.4.0]</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>364.8938</v>
+        <v>-464.7225</v>
       </c>
       <c r="C37" t="n">
-        <v>-304.0984</v>
+        <v>-2619.4738</v>
       </c>
       <c r="D37" t="n">
-        <v>1033.8859</v>
+        <v>1690.0288</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>0.672</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C(pathologic_N)[T.2.0]</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>286.9821</v>
+        <v>27.6948</v>
       </c>
       <c r="C38" t="n">
-        <v>-841.8081</v>
+        <v>-20.9676</v>
       </c>
       <c r="D38" t="n">
-        <v>1415.7724</v>
+        <v>76.3571</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.617</t>
+          <t>0.264</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C(pathologic_N)[T.3.0]</t>
+          <t>number_pack_years_smoked</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1423.1931</v>
+        <v>0.6273</v>
       </c>
       <c r="C39" t="n">
-        <v>-3440.2646</v>
+        <v>-12.3343</v>
       </c>
       <c r="D39" t="n">
-        <v>593.8784000000001</v>
+        <v>13.589</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>0.924</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>29.1434</v>
-      </c>
-      <c r="C40" t="n">
-        <v>2.6672</v>
-      </c>
-      <c r="D40" t="n">
-        <v>55.6197</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0.031</t>
-        </is>
-      </c>
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>0.0539</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-6.9384</v>
-      </c>
-      <c r="D41" t="n">
-        <v>7.0462</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0.988</t>
-        </is>
-      </c>
+      <c r="A41">
+        <f>== [ Model: Base + Pathologic N ] ===</f>
+        <v/>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>pathologic_stage</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>-161.0707</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-603.7436</v>
-      </c>
-      <c r="D42" t="n">
-        <v>281.6022</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0.475</t>
-        </is>
-      </c>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>FAT1expression</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>FAT1expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_N)</t>
+        </is>
+      </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44">
-        <f>== [ Model: Base + Pathologic M ] ===</f>
-        <v/>
-      </c>
-      <c r="B44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0.0094</t>
+        </is>
+      </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
@@ -2753,12 +2595,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Dependent Variable (Y)</t>
+          <t>Prob (F-statistic)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FAT1expression</t>
+          <t>7.0437e-01</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -2768,14 +2610,10 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>FAT1expression ~ age + number_pack_years_smoked + pathologic_stage + C(gender) + C(pathologic_M)</t>
-        </is>
-      </c>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
@@ -2783,176 +2621,349 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>0.0207</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2569.1414</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-953.1477</v>
+      </c>
+      <c r="D47" t="n">
+        <v>6091.4305</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.152</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2.5655e-01</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>150.9179</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-774.0045</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1075.8403</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.749</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+          <t>C(pathologic_N)[T.1.0]</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>221.606</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-718.1913</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1161.4033</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.643</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Intercept</t>
+          <t>C(pathologic_N)[T.2.0]</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1198.7172</v>
+        <v>-246.3987</v>
       </c>
       <c r="C50" t="n">
-        <v>-991.3101</v>
+        <v>-1765.8405</v>
       </c>
       <c r="D50" t="n">
-        <v>3388.7445</v>
+        <v>1273.043</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>0.750</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>C(gender)[T.MALE]</t>
+          <t>C(pathologic_N)[T.3.0]</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>374.5121</v>
+        <v>-2618.6068</v>
       </c>
       <c r="C51" t="n">
-        <v>-168.5072</v>
+        <v>-6307.8723</v>
       </c>
       <c r="D51" t="n">
-        <v>917.5314</v>
+        <v>1070.6586</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.164</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>C(pathologic_M)[T.1.0]</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-10.19</v>
+        <v>28.3491</v>
       </c>
       <c r="C52" t="n">
-        <v>-2257.5408</v>
+        <v>-21.4907</v>
       </c>
       <c r="D52" t="n">
-        <v>2237.1608</v>
+        <v>78.1889</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0.993</t>
+          <t>0.264</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>number_pack_years_smoked</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>32.0019</v>
+        <v>0.4045</v>
       </c>
       <c r="C53" t="n">
-        <v>2.4734</v>
+        <v>-12.6281</v>
       </c>
       <c r="D53" t="n">
-        <v>61.5303</v>
+        <v>13.437</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>0.951</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>1.6448</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-6.2088</v>
-      </c>
-      <c r="D54" t="n">
-        <v>9.4983</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0.681</t>
-        </is>
-      </c>
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>pathologic_stage</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>-2.463</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-316.7788</v>
-      </c>
-      <c r="D55" t="n">
-        <v>311.8528</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>0.988</t>
-        </is>
-      </c>
+      <c r="A55">
+        <f>== [ Model: Base + Pathologic M ] ===</f>
+        <v/>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>FAT1expression</t>
+        </is>
+      </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>FAT1expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_M)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0.0089</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>5.4751e-01</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>2668.6045</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-1274.244</v>
+      </c>
+      <c r="D61" t="n">
+        <v>6611.453</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0.184</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>127.4343</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-919.4857</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1174.3544</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0.811</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>C(pathologic_M)[T.1.0]</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2500.7483</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-974.0025000000001</v>
+      </c>
+      <c r="D63" t="n">
+        <v>5975.4992</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0.158</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>24.7838</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-31.2446</v>
+      </c>
+      <c r="D64" t="n">
+        <v>80.81229999999999</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0.385</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>2.1383</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-12.5999</v>
+      </c>
+      <c r="D65" t="n">
+        <v>16.8765</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0.776</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3013,12 +3024,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.423</t>
+          <t>3.659</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.120</t>
+          <t>0.056</t>
         </is>
       </c>
     </row>
@@ -3040,12 +3051,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.487</t>
+          <t>3.152</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>0.076</t>
         </is>
       </c>
     </row>

--- a/result/FAT1_LUSC_Tables.xlsx
+++ b/result/FAT1_LUSC_Tables.xlsx
@@ -10,8 +10,9 @@
     <sheet name="Table 1 (Chi-square)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Table 2 (Correlation)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Table 3 (Cox)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Table 4 (Multivariate OLS)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Table 5 (KM Log-rank)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Table 3.1 (Cox)_stage_continuous" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Table 4 (Multivariate OLS)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Table 5 (KM Log-rank)" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1865,18 +1866,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Variable</t>
+          <t>Clinical Variable</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Coefficient</t>
+          <t>Hazard Ratio (HR)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -1896,1074 +1897,109 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <f>== [ Model: Base Model (No Stage) ] ===</f>
-        <v/>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.021</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.027</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>FAT1expression</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.975</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>FAT1expression ~ age + number_pack_years_smoked + C(gender)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>pathologic_stage</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.201</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.439</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.048</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.0035</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+          <t>FAT1group_Low</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.041</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>6.9624e-01</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2567.2399</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-816.0096</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5950.4894</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0.137</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>139.162</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-777.7317</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1056.0557</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.766</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>28.2069</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-20.2</v>
-      </c>
-      <c r="D10" t="n">
-        <v>76.6139</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.253</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.9254</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-11.9866</v>
-      </c>
-      <c r="D11" t="n">
-        <v>13.8375</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.888</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13">
-        <f>== [ Model: Base + Pathologic Stage ] ===</f>
-        <v/>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>FAT1expression</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>FAT1expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_stage)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0.0181</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2.8871e-01</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2588.9245</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-884.619</v>
-      </c>
-      <c r="D19" t="n">
-        <v>6062.468</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0.144</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>72.7373</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-849.0967000000001</v>
-      </c>
-      <c r="D20" t="n">
-        <v>994.5713</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0.877</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>C(pathologic_stage)[T.2.0]</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>614.3365</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-301.0698</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1529.7428</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0.188</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>C(pathologic_stage)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>-562.1844</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-1702.6774</v>
-      </c>
-      <c r="D22" t="n">
-        <v>578.3086</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>C(pathologic_stage)[T.4.0]</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>2564.0666</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-812.3525</v>
-      </c>
-      <c r="D23" t="n">
-        <v>5940.4856</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0.136</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>26.3274</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-22.5987</v>
-      </c>
-      <c r="D24" t="n">
-        <v>75.2535</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0.291</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1.2873</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-11.6663</v>
-      </c>
-      <c r="D25" t="n">
-        <v>14.2408</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0.845</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27">
-        <f>== [ Model: Base + Pathologic T ] ===</f>
-        <v/>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>FAT1expression</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>FAT1expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_T)</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>0.0071</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>8.2118e-01</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>2951.5437</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-503.003</v>
-      </c>
-      <c r="D33" t="n">
-        <v>6406.0904</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0.094</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>173.4211</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-757.5424</v>
-      </c>
-      <c r="D34" t="n">
-        <v>1104.3846</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0.714</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.2.0]</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>-384.7719</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-1380.9682</v>
-      </c>
-      <c r="D35" t="n">
-        <v>611.4244</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>0.448</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>-852.4938</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-2260.3518</v>
-      </c>
-      <c r="D36" t="n">
-        <v>555.3643</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0.235</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.4.0]</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>-464.7225</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-2619.4738</v>
-      </c>
-      <c r="D37" t="n">
-        <v>1690.0288</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0.672</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>27.6948</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-20.9676</v>
-      </c>
-      <c r="D38" t="n">
-        <v>76.3571</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0.264</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>0.6273</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-12.3343</v>
-      </c>
-      <c r="D39" t="n">
-        <v>13.589</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0.924</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <f>== [ Model: Base + Pathologic N ] ===</f>
-        <v/>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>FAT1expression</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>FAT1expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_N)</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>0.0094</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>7.0437e-01</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>2569.1414</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-953.1477</v>
-      </c>
-      <c r="D47" t="n">
-        <v>6091.4305</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>0.152</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>150.9179</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-774.0045</v>
-      </c>
-      <c r="D48" t="n">
-        <v>1075.8403</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>0.749</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.1.0]</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>221.606</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-718.1913</v>
-      </c>
-      <c r="D49" t="n">
-        <v>1161.4033</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>0.643</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.2.0]</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>-246.3987</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-1765.8405</v>
-      </c>
-      <c r="D50" t="n">
-        <v>1273.043</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>0.750</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>-2618.6068</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-6307.8723</v>
-      </c>
-      <c r="D51" t="n">
-        <v>1070.6586</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0.164</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>28.3491</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-21.4907</v>
-      </c>
-      <c r="D52" t="n">
-        <v>78.1889</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0.264</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>0.4045</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-12.6281</v>
-      </c>
-      <c r="D53" t="n">
-        <v>13.437</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0.951</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <f>== [ Model: Base + Pathologic M ] ===</f>
-        <v/>
-      </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>FAT1expression</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>FAT1expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_M)</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>0.0089</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>5.4751e-01</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>2668.6045</v>
-      </c>
-      <c r="C61" t="n">
-        <v>-1274.244</v>
-      </c>
-      <c r="D61" t="n">
-        <v>6611.453</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>0.184</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>127.4343</v>
-      </c>
-      <c r="C62" t="n">
-        <v>-919.4857</v>
-      </c>
-      <c r="D62" t="n">
-        <v>1174.3544</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>0.811</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>C(pathologic_M)[T.1.0]</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>2500.7483</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-974.0025000000001</v>
-      </c>
-      <c r="D63" t="n">
-        <v>5975.4992</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>0.158</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>24.7838</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-31.2446</v>
-      </c>
-      <c r="D64" t="n">
-        <v>80.81229999999999</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>0.385</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>2.1383</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-12.5999</v>
-      </c>
-      <c r="D65" t="n">
-        <v>16.8765</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>0.776</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
+          <t>gender_MALE</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.231</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.741</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.239</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2976,6 +2012,1047 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Coefficient</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <f>== [ Model: Base Model (No Stage) ] ===</f>
+        <v/>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FAT1expression</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FAT1expression ~ age + number_pack_years_smoked + C(gender)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.0035</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>6.9624e-01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2567.24</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>-816.01-5950.489</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.137</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>139.162</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-777.732-1056.056</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.766</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>28.207</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-20.2-76.614</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.253</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-11.987-13.837</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.888</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <f>== [ Model: Base + Pathologic Stage ] ===</f>
+        <v/>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>FAT1expression</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>FAT1expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_stage)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0.0181</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2.8871e-01</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2588.925</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>-884.619-6062.468</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.144</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>72.73699999999999</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-849.097-994.571</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0.877</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>C(pathologic_stage)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>614.337</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-301.07-1529.743</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0.188</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>C(pathologic_stage)[T.3.0]</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>-562.184</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-1702.677-578.309</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>C(pathologic_stage)[T.4.0]</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2564.067</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-812.353-5940.486</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0.136</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>26.327</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>-22.599-75.254</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.291</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1.287</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>-11.666-14.241</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0.845</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <f>== [ Model: Base + Pathologic T ] ===</f>
+        <v/>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FAT1expression</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FAT1expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_T)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0.0071</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>8.2118e-01</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2951.544</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>-503.003-6406.09</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>0.094</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>173.421</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>-757.542-1104.385</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>0.714</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>-384.772</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>-1380.968-611.424</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>0.448</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.3.0]</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>-852.494</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>-2260.352-555.364</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>0.235</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.4.0]</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-464.722</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>-2619.474-1690.029</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>0.672</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>27.695</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>-20.968-76.357</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0.264</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>-12.334-13.589</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>0.924</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <f>== [ Model: Base + Pathologic N ] ===</f>
+        <v/>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>FAT1expression</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>FAT1expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_N)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0.0094</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>7.0437e-01</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2569.141</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>-953.148-6091.43</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.152</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>150.918</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>-774.004-1075.84</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.749</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.1.0]</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>221.606</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>-718.191-1161.403</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.643</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>-246.399</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>-1765.84-1273.043</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.3.0]</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>-2618.607</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>-6307.872-1070.659</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.164</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>28.349</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>-21.491-78.189</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.264</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>-12.628-13.437</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>0.951</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <f>== [ Model: Base + Pathologic M ] ===</f>
+        <v/>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>FAT1expression</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>FAT1expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_M)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0.0089</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>5.4751e-01</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>2668.605</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>-1274.244-6611.453</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>0.184</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>127.434</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>-919.486-1174.354</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>0.811</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>C(pathologic_M)[T.1.0]</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2500.748</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>-974.003-5975.499</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>0.158</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>24.784</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>-31.245-80.812</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>0.385</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>2.138</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>-12.6-16.876</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>0.776</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/result/FAT1_LUSC_Tables.xlsx
+++ b/result/FAT1_LUSC_Tables.xlsx
@@ -1678,7 +1678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1694,15 +1694,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>95% CI Lower</t>
+          <t>95% CI</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI Upper</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -1717,13 +1712,28 @@
       <c r="B2" t="n">
         <v>1.02</v>
       </c>
-      <c r="C2" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.039</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>covariate
+age                         1.001
+number_pack_years_smoked    0.996
+FAT1group_Low               0.537
+gender_MALE                 0.858
+pathologic_stage_2.0        0.706
+pathologic_stage_3.0        0.912
+pathologic_stage_4.0        1.262
+Name: exp(coef) lower 95%, dtype: float64-covariate
+age                         1.039
+number_pack_years_smoked    1.005
+FAT1group_Low               0.972
+gender_MALE                 1.726
+pathologic_stage_2.0        1.422
+pathologic_stage_3.0        2.014
+pathologic_stage_4.0        7.896
+Name: exp(coef) upper 95%, dtype: float64</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>0.038</t>
         </is>
@@ -1738,13 +1748,28 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.996</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.005</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>covariate
+age                         1.001
+number_pack_years_smoked    0.996
+FAT1group_Low               0.537
+gender_MALE                 0.858
+pathologic_stage_2.0        0.706
+pathologic_stage_3.0        0.912
+pathologic_stage_4.0        1.262
+Name: exp(coef) lower 95%, dtype: float64-covariate
+age                         1.039
+number_pack_years_smoked    1.005
+FAT1group_Low               0.972
+gender_MALE                 1.726
+pathologic_stage_2.0        1.422
+pathologic_stage_3.0        2.014
+pathologic_stage_4.0        7.896
+Name: exp(coef) upper 95%, dtype: float64</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>0.891</t>
         </is>
@@ -1759,13 +1784,28 @@
       <c r="B4" t="n">
         <v>0.723</v>
       </c>
-      <c r="C4" t="n">
-        <v>0.537</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.972</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>covariate
+age                         1.001
+number_pack_years_smoked    0.996
+FAT1group_Low               0.537
+gender_MALE                 0.858
+pathologic_stage_2.0        0.706
+pathologic_stage_3.0        0.912
+pathologic_stage_4.0        1.262
+Name: exp(coef) lower 95%, dtype: float64-covariate
+age                         1.039
+number_pack_years_smoked    1.005
+FAT1group_Low               0.972
+gender_MALE                 1.726
+pathologic_stage_2.0        1.422
+pathologic_stage_3.0        2.014
+pathologic_stage_4.0        7.896
+Name: exp(coef) upper 95%, dtype: float64</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>0.032</t>
         </is>
@@ -1780,13 +1820,28 @@
       <c r="B5" t="n">
         <v>1.217</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.858</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.726</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>covariate
+age                         1.001
+number_pack_years_smoked    0.996
+FAT1group_Low               0.537
+gender_MALE                 0.858
+pathologic_stage_2.0        0.706
+pathologic_stage_3.0        0.912
+pathologic_stage_4.0        1.262
+Name: exp(coef) lower 95%, dtype: float64-covariate
+age                         1.039
+number_pack_years_smoked    1.005
+FAT1group_Low               0.972
+gender_MALE                 1.726
+pathologic_stage_2.0        1.422
+pathologic_stage_3.0        2.014
+pathologic_stage_4.0        7.896
+Name: exp(coef) upper 95%, dtype: float64</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>0.270</t>
         </is>
@@ -1801,13 +1856,28 @@
       <c r="B6" t="n">
         <v>1.002</v>
       </c>
-      <c r="C6" t="n">
-        <v>0.706</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.422</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>covariate
+age                         1.001
+number_pack_years_smoked    0.996
+FAT1group_Low               0.537
+gender_MALE                 0.858
+pathologic_stage_2.0        0.706
+pathologic_stage_3.0        0.912
+pathologic_stage_4.0        1.262
+Name: exp(coef) lower 95%, dtype: float64-covariate
+age                         1.039
+number_pack_years_smoked    1.005
+FAT1group_Low               0.972
+gender_MALE                 1.726
+pathologic_stage_2.0        1.422
+pathologic_stage_3.0        2.014
+pathologic_stage_4.0        7.896
+Name: exp(coef) upper 95%, dtype: float64</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>0.990</t>
         </is>
@@ -1822,13 +1892,28 @@
       <c r="B7" t="n">
         <v>1.355</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.912</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2.014</v>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>covariate
+age                         1.001
+number_pack_years_smoked    0.996
+FAT1group_Low               0.537
+gender_MALE                 0.858
+pathologic_stage_2.0        0.706
+pathologic_stage_3.0        0.912
+pathologic_stage_4.0        1.262
+Name: exp(coef) lower 95%, dtype: float64-covariate
+age                         1.039
+number_pack_years_smoked    1.005
+FAT1group_Low               0.972
+gender_MALE                 1.726
+pathologic_stage_2.0        1.422
+pathologic_stage_3.0        2.014
+pathologic_stage_4.0        7.896
+Name: exp(coef) upper 95%, dtype: float64</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>0.132</t>
         </is>
@@ -1843,13 +1928,28 @@
       <c r="B8" t="n">
         <v>3.157</v>
       </c>
-      <c r="C8" t="n">
-        <v>1.262</v>
-      </c>
-      <c r="D8" t="n">
-        <v>7.896</v>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>covariate
+age                         1.001
+number_pack_years_smoked    0.996
+FAT1group_Low               0.537
+gender_MALE                 0.858
+pathologic_stage_2.0        0.706
+pathologic_stage_3.0        0.912
+pathologic_stage_4.0        1.262
+Name: exp(coef) lower 95%, dtype: float64-covariate
+age                         1.039
+number_pack_years_smoked    1.005
+FAT1group_Low               0.972
+gender_MALE                 1.726
+pathologic_stage_2.0        1.422
+pathologic_stage_3.0        2.014
+pathologic_stage_4.0        7.896
+Name: exp(coef) upper 95%, dtype: float64</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>0.014</t>
         </is>
@@ -1866,7 +1966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1882,15 +1982,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>95% CI Lower</t>
+          <t>95% CI</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI Upper</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -1905,13 +2000,24 @@
       <c r="B2" t="n">
         <v>1.021</v>
       </c>
-      <c r="C2" t="n">
-        <v>1.002</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>covariate
+age                         1.002
+number_pack_years_smoked    0.995
+pathologic_stage            1.002
+FAT1group_Low               0.547
+gender_MALE                 0.871
+Name: exp(coef) lower 95%, dtype: float64-covariate
+age                         1.040
+number_pack_years_smoked    1.005
+pathologic_stage            1.439
+FAT1group_Low               0.987
+gender_MALE                 1.741
+Name: exp(coef) upper 95%, dtype: float64</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>0.027</t>
         </is>
@@ -1926,13 +2032,24 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.995</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.005</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>covariate
+age                         1.002
+number_pack_years_smoked    0.995
+pathologic_stage            1.002
+FAT1group_Low               0.547
+gender_MALE                 0.871
+Name: exp(coef) lower 95%, dtype: float64-covariate
+age                         1.040
+number_pack_years_smoked    1.005
+pathologic_stage            1.439
+FAT1group_Low               0.987
+gender_MALE                 1.741
+Name: exp(coef) upper 95%, dtype: float64</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>0.975</t>
         </is>
@@ -1947,13 +2064,24 @@
       <c r="B4" t="n">
         <v>1.201</v>
       </c>
-      <c r="C4" t="n">
-        <v>1.002</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.439</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>covariate
+age                         1.002
+number_pack_years_smoked    0.995
+pathologic_stage            1.002
+FAT1group_Low               0.547
+gender_MALE                 0.871
+Name: exp(coef) lower 95%, dtype: float64-covariate
+age                         1.040
+number_pack_years_smoked    1.005
+pathologic_stage            1.439
+FAT1group_Low               0.987
+gender_MALE                 1.741
+Name: exp(coef) upper 95%, dtype: float64</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>0.048</t>
         </is>
@@ -1968,13 +2096,24 @@
       <c r="B5" t="n">
         <v>0.735</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.547</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.987</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>covariate
+age                         1.002
+number_pack_years_smoked    0.995
+pathologic_stage            1.002
+FAT1group_Low               0.547
+gender_MALE                 0.871
+Name: exp(coef) lower 95%, dtype: float64-covariate
+age                         1.040
+number_pack_years_smoked    1.005
+pathologic_stage            1.439
+FAT1group_Low               0.987
+gender_MALE                 1.741
+Name: exp(coef) upper 95%, dtype: float64</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>0.041</t>
         </is>
@@ -1989,13 +2128,24 @@
       <c r="B6" t="n">
         <v>1.231</v>
       </c>
-      <c r="C6" t="n">
-        <v>0.871</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.741</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>covariate
+age                         1.002
+number_pack_years_smoked    0.995
+pathologic_stage            1.002
+FAT1group_Low               0.547
+gender_MALE                 0.871
+Name: exp(coef) lower 95%, dtype: float64-covariate
+age                         1.040
+number_pack_years_smoked    1.005
+pathologic_stage            1.439
+FAT1group_Low               0.987
+gender_MALE                 1.741
+Name: exp(coef) upper 95%, dtype: float64</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>0.239</t>
         </is>

--- a/result/FAT1_LUSC_Tables.xlsx
+++ b/result/FAT1_LUSC_Tables.xlsx
@@ -1714,23 +1714,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>covariate
-age                         1.001
-number_pack_years_smoked    0.996
-FAT1group_Low               0.537
-gender_MALE                 0.858
-pathologic_stage_2.0        0.706
-pathologic_stage_3.0        0.912
-pathologic_stage_4.0        1.262
-Name: exp(coef) lower 95%, dtype: float64-covariate
-age                         1.039
-number_pack_years_smoked    1.005
-FAT1group_Low               0.972
-gender_MALE                 1.726
-pathologic_stage_2.0        1.422
-pathologic_stage_3.0        2.014
-pathologic_stage_4.0        7.896
-Name: exp(coef) upper 95%, dtype: float64</t>
+          <t>1.001-1.039</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1750,23 +1734,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>covariate
-age                         1.001
-number_pack_years_smoked    0.996
-FAT1group_Low               0.537
-gender_MALE                 0.858
-pathologic_stage_2.0        0.706
-pathologic_stage_3.0        0.912
-pathologic_stage_4.0        1.262
-Name: exp(coef) lower 95%, dtype: float64-covariate
-age                         1.039
-number_pack_years_smoked    1.005
-FAT1group_Low               0.972
-gender_MALE                 1.726
-pathologic_stage_2.0        1.422
-pathologic_stage_3.0        2.014
-pathologic_stage_4.0        7.896
-Name: exp(coef) upper 95%, dtype: float64</t>
+          <t>0.996-1.005</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1786,23 +1754,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>covariate
-age                         1.001
-number_pack_years_smoked    0.996
-FAT1group_Low               0.537
-gender_MALE                 0.858
-pathologic_stage_2.0        0.706
-pathologic_stage_3.0        0.912
-pathologic_stage_4.0        1.262
-Name: exp(coef) lower 95%, dtype: float64-covariate
-age                         1.039
-number_pack_years_smoked    1.005
-FAT1group_Low               0.972
-gender_MALE                 1.726
-pathologic_stage_2.0        1.422
-pathologic_stage_3.0        2.014
-pathologic_stage_4.0        7.896
-Name: exp(coef) upper 95%, dtype: float64</t>
+          <t>0.537-0.972</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1822,23 +1774,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>covariate
-age                         1.001
-number_pack_years_smoked    0.996
-FAT1group_Low               0.537
-gender_MALE                 0.858
-pathologic_stage_2.0        0.706
-pathologic_stage_3.0        0.912
-pathologic_stage_4.0        1.262
-Name: exp(coef) lower 95%, dtype: float64-covariate
-age                         1.039
-number_pack_years_smoked    1.005
-FAT1group_Low               0.972
-gender_MALE                 1.726
-pathologic_stage_2.0        1.422
-pathologic_stage_3.0        2.014
-pathologic_stage_4.0        7.896
-Name: exp(coef) upper 95%, dtype: float64</t>
+          <t>0.858-1.726</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1858,23 +1794,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>covariate
-age                         1.001
-number_pack_years_smoked    0.996
-FAT1group_Low               0.537
-gender_MALE                 0.858
-pathologic_stage_2.0        0.706
-pathologic_stage_3.0        0.912
-pathologic_stage_4.0        1.262
-Name: exp(coef) lower 95%, dtype: float64-covariate
-age                         1.039
-number_pack_years_smoked    1.005
-FAT1group_Low               0.972
-gender_MALE                 1.726
-pathologic_stage_2.0        1.422
-pathologic_stage_3.0        2.014
-pathologic_stage_4.0        7.896
-Name: exp(coef) upper 95%, dtype: float64</t>
+          <t>0.706-1.422</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1894,23 +1814,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>covariate
-age                         1.001
-number_pack_years_smoked    0.996
-FAT1group_Low               0.537
-gender_MALE                 0.858
-pathologic_stage_2.0        0.706
-pathologic_stage_3.0        0.912
-pathologic_stage_4.0        1.262
-Name: exp(coef) lower 95%, dtype: float64-covariate
-age                         1.039
-number_pack_years_smoked    1.005
-FAT1group_Low               0.972
-gender_MALE                 1.726
-pathologic_stage_2.0        1.422
-pathologic_stage_3.0        2.014
-pathologic_stage_4.0        7.896
-Name: exp(coef) upper 95%, dtype: float64</t>
+          <t>0.912-2.014</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1930,23 +1834,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>covariate
-age                         1.001
-number_pack_years_smoked    0.996
-FAT1group_Low               0.537
-gender_MALE                 0.858
-pathologic_stage_2.0        0.706
-pathologic_stage_3.0        0.912
-pathologic_stage_4.0        1.262
-Name: exp(coef) lower 95%, dtype: float64-covariate
-age                         1.039
-number_pack_years_smoked    1.005
-FAT1group_Low               0.972
-gender_MALE                 1.726
-pathologic_stage_2.0        1.422
-pathologic_stage_3.0        2.014
-pathologic_stage_4.0        7.896
-Name: exp(coef) upper 95%, dtype: float64</t>
+          <t>1.262-7.896</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2002,19 +1890,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>covariate
-age                         1.002
-number_pack_years_smoked    0.995
-pathologic_stage            1.002
-FAT1group_Low               0.547
-gender_MALE                 0.871
-Name: exp(coef) lower 95%, dtype: float64-covariate
-age                         1.040
-number_pack_years_smoked    1.005
-pathologic_stage            1.439
-FAT1group_Low               0.987
-gender_MALE                 1.741
-Name: exp(coef) upper 95%, dtype: float64</t>
+          <t>1.002-1.040</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2034,19 +1910,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>covariate
-age                         1.002
-number_pack_years_smoked    0.995
-pathologic_stage            1.002
-FAT1group_Low               0.547
-gender_MALE                 0.871
-Name: exp(coef) lower 95%, dtype: float64-covariate
-age                         1.040
-number_pack_years_smoked    1.005
-pathologic_stage            1.439
-FAT1group_Low               0.987
-gender_MALE                 1.741
-Name: exp(coef) upper 95%, dtype: float64</t>
+          <t>0.995-1.005</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2066,19 +1930,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>covariate
-age                         1.002
-number_pack_years_smoked    0.995
-pathologic_stage            1.002
-FAT1group_Low               0.547
-gender_MALE                 0.871
-Name: exp(coef) lower 95%, dtype: float64-covariate
-age                         1.040
-number_pack_years_smoked    1.005
-pathologic_stage            1.439
-FAT1group_Low               0.987
-gender_MALE                 1.741
-Name: exp(coef) upper 95%, dtype: float64</t>
+          <t>1.002-1.439</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2098,19 +1950,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>covariate
-age                         1.002
-number_pack_years_smoked    0.995
-pathologic_stage            1.002
-FAT1group_Low               0.547
-gender_MALE                 0.871
-Name: exp(coef) lower 95%, dtype: float64-covariate
-age                         1.040
-number_pack_years_smoked    1.005
-pathologic_stage            1.439
-FAT1group_Low               0.987
-gender_MALE                 1.741
-Name: exp(coef) upper 95%, dtype: float64</t>
+          <t>0.547-0.987</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2130,19 +1970,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>covariate
-age                         1.002
-number_pack_years_smoked    0.995
-pathologic_stage            1.002
-FAT1group_Low               0.547
-gender_MALE                 0.871
-Name: exp(coef) lower 95%, dtype: float64-covariate
-age                         1.040
-number_pack_years_smoked    1.005
-pathologic_stage            1.439
-FAT1group_Low               0.987
-gender_MALE                 1.741
-Name: exp(coef) upper 95%, dtype: float64</t>
+          <t>0.871-1.741</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">

--- a/result/FAT1_LUSC_Tables.xlsx
+++ b/result/FAT1_LUSC_Tables.xlsx
@@ -3079,12 +3079,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.659</t>
+          <t>7.681</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>0.053</t>
         </is>
       </c>
     </row>
@@ -3106,12 +3106,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.152</t>
+          <t>3.279</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>0.351</t>
         </is>
       </c>
     </row>
